--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>219</v>
+        <v>76</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>297</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>277</v>
       </c>
       <c r="D3">
-        <v>313</v>
+        <v>103</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="G3">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D2">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="E2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D3">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E3">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>
